--- a/config/Localization/LocalizationTable.xlsx
+++ b/config/Localization/LocalizationTable.xlsx
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,6 +130,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F386"/>
+  <dimension ref="A1:F424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9033,674 +9036,674 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B305" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C305" s="18" t="n"/>
-      <c r="D305" s="18" t="inlineStr">
-        <is>
-          <t>新手之臂</t>
-        </is>
-      </c>
-      <c r="E305" s="18" t="inlineStr">
-        <is>
-          <t>新手之臂</t>
-        </is>
-      </c>
-      <c r="F305" s="18" t="inlineStr">
-        <is>
-          <t>Rookie Arm</t>
+      <c r="A305" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B305" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEMap·ZhName</t>
+        </is>
+      </c>
+      <c r="C305" s="20" t="inlineStr"/>
+      <c r="D305" s="20" t="inlineStr">
+        <is>
+          <t>初阵</t>
+        </is>
+      </c>
+      <c r="E305" s="20" t="inlineStr">
+        <is>
+          <t>初阵</t>
+        </is>
+      </c>
+      <c r="F305" s="20" t="inlineStr">
+        <is>
+          <t>First Battle</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B306" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C306" s="18" t="n"/>
-      <c r="D306" s="18" t="inlineStr">
-        <is>
-          <t>深渊之臂</t>
-        </is>
-      </c>
-      <c r="E306" s="18" t="inlineStr">
-        <is>
-          <t>深渊之臂</t>
-        </is>
-      </c>
-      <c r="F306" s="18" t="inlineStr">
-        <is>
-          <t>Abyss Arm</t>
+      <c r="A306" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B306" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C306" s="20" t="inlineStr"/>
+      <c r="D306" s="20" t="inlineStr">
+        <is>
+          <t>桥梁</t>
+        </is>
+      </c>
+      <c r="E306" s="20" t="inlineStr">
+        <is>
+          <t>桥梁</t>
+        </is>
+      </c>
+      <c r="F306" s="20" t="inlineStr">
+        <is>
+          <t>Bridge</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B307" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C307" s="18" t="n"/>
-      <c r="D307" s="18" t="inlineStr">
-        <is>
-          <t>烈焰之臂</t>
-        </is>
-      </c>
-      <c r="E307" s="18" t="inlineStr">
-        <is>
-          <t>烈焰之臂</t>
-        </is>
-      </c>
-      <c r="F307" s="18" t="inlineStr">
-        <is>
-          <t>Flame Arm</t>
+      <c r="A307" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B307" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C307" s="20" t="inlineStr"/>
+      <c r="D307" s="20" t="inlineStr">
+        <is>
+          <t>兵营</t>
+        </is>
+      </c>
+      <c r="E307" s="20" t="inlineStr">
+        <is>
+          <t>兵营</t>
+        </is>
+      </c>
+      <c r="F307" s="20" t="inlineStr">
+        <is>
+          <t>Barracks</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B308" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C308" s="18" t="n"/>
-      <c r="D308" s="18" t="inlineStr">
-        <is>
-          <t>紫晶之臂</t>
-        </is>
-      </c>
-      <c r="E308" s="18" t="inlineStr">
-        <is>
-          <t>紫晶之臂</t>
-        </is>
-      </c>
-      <c r="F308" s="18" t="inlineStr">
-        <is>
-          <t>Amethyst Arm</t>
+      <c r="A308" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B308" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C308" s="20" t="inlineStr"/>
+      <c r="D308" s="20" t="inlineStr">
+        <is>
+          <t>平地</t>
+        </is>
+      </c>
+      <c r="E308" s="20" t="inlineStr">
+        <is>
+          <t>平地</t>
+        </is>
+      </c>
+      <c r="F308" s="20" t="inlineStr">
+        <is>
+          <t>Plains</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B309" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C309" s="18" t="n"/>
-      <c r="D309" s="18" t="inlineStr">
-        <is>
-          <t>结实之臂</t>
-        </is>
-      </c>
-      <c r="E309" s="18" t="inlineStr">
-        <is>
-          <t>结实之臂</t>
-        </is>
-      </c>
-      <c r="F309" s="18" t="inlineStr">
-        <is>
-          <t>Sturdy Arm</t>
+      <c r="A309" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B309" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C309" s="20" t="inlineStr"/>
+      <c r="D309" s="20" t="inlineStr">
+        <is>
+          <t>村庄</t>
+        </is>
+      </c>
+      <c r="E309" s="20" t="inlineStr">
+        <is>
+          <t>村庄</t>
+        </is>
+      </c>
+      <c r="F309" s="20" t="inlineStr">
+        <is>
+          <t>Village</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B310" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C310" s="18" t="n"/>
-      <c r="D310" s="18" t="inlineStr">
-        <is>
-          <t>翡翠之臂</t>
-        </is>
-      </c>
-      <c r="E310" s="18" t="inlineStr">
-        <is>
-          <t>翡翠之臂</t>
-        </is>
-      </c>
-      <c r="F310" s="18" t="inlineStr">
-        <is>
-          <t>Jade Arm</t>
+      <c r="A310" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B310" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C310" s="20" t="inlineStr"/>
+      <c r="D310" s="20" t="inlineStr">
+        <is>
+          <t>山地</t>
+        </is>
+      </c>
+      <c r="E310" s="20" t="inlineStr">
+        <is>
+          <t>山地</t>
+        </is>
+      </c>
+      <c r="F310" s="20" t="inlineStr">
+        <is>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B311" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C311" s="18" t="n"/>
-      <c r="D311" s="18" t="inlineStr">
-        <is>
-          <t>钢铁之臂</t>
-        </is>
-      </c>
-      <c r="E311" s="18" t="inlineStr">
-        <is>
-          <t>钢铁之臂</t>
-        </is>
-      </c>
-      <c r="F311" s="18" t="inlineStr">
-        <is>
-          <t>Steel Arm</t>
+      <c r="A311" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B311" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C311" s="20" t="inlineStr"/>
+      <c r="D311" s="20" t="inlineStr">
+        <is>
+          <t>丘陵</t>
+        </is>
+      </c>
+      <c r="E311" s="20" t="inlineStr">
+        <is>
+          <t>丘陵</t>
+        </is>
+      </c>
+      <c r="F311" s="20" t="inlineStr">
+        <is>
+          <t>Hill</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B312" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C312" s="18" t="n"/>
-      <c r="D312" s="18" t="inlineStr">
-        <is>
-          <t>雷霆之臂</t>
-        </is>
-      </c>
-      <c r="E312" s="18" t="inlineStr">
-        <is>
-          <t>雷霆之臂</t>
-        </is>
-      </c>
-      <c r="F312" s="18" t="inlineStr">
-        <is>
-          <t>Thunder Arm</t>
+      <c r="A312" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B312" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C312" s="20" t="inlineStr"/>
+      <c r="D312" s="20" t="inlineStr">
+        <is>
+          <t>城堡</t>
+        </is>
+      </c>
+      <c r="E312" s="20" t="inlineStr">
+        <is>
+          <t>城堡</t>
+        </is>
+      </c>
+      <c r="F312" s="20" t="inlineStr">
+        <is>
+          <t>Castle</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B313" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWArm·ZhName</t>
-        </is>
-      </c>
-      <c r="C313" s="18" t="n"/>
-      <c r="D313" s="18" t="inlineStr">
-        <is>
-          <t>青铜之臂</t>
-        </is>
-      </c>
-      <c r="E313" s="18" t="inlineStr">
-        <is>
-          <t>青铜之臂</t>
-        </is>
-      </c>
-      <c r="F313" s="18" t="inlineStr">
-        <is>
-          <t>Bronze Arm</t>
+      <c r="A313" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B313" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C313" s="20" t="inlineStr"/>
+      <c r="D313" s="20" t="inlineStr">
+        <is>
+          <t>森林</t>
+        </is>
+      </c>
+      <c r="E313" s="20" t="inlineStr">
+        <is>
+          <t>森林</t>
+        </is>
+      </c>
+      <c r="F313" s="20" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B314" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C314" s="18" t="n"/>
-      <c r="D314" s="18" t="inlineStr">
-        <is>
-          <t>仙人掌之王</t>
-        </is>
-      </c>
-      <c r="E314" s="18" t="inlineStr">
-        <is>
-          <t>仙人掌之王</t>
-        </is>
-      </c>
-      <c r="F314" s="18" t="inlineStr">
-        <is>
-          <t>Cactus King</t>
+      <c r="A314" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B314" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C314" s="20" t="inlineStr"/>
+      <c r="D314" s="20" t="inlineStr">
+        <is>
+          <t>水面</t>
+        </is>
+      </c>
+      <c r="E314" s="20" t="inlineStr">
+        <is>
+          <t>水面</t>
+        </is>
+      </c>
+      <c r="F314" s="20" t="inlineStr">
+        <is>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B315" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C315" s="18" t="n"/>
-      <c r="D315" s="18" t="inlineStr">
-        <is>
-          <t>仙人掌战士</t>
-        </is>
-      </c>
-      <c r="E315" s="18" t="inlineStr">
-        <is>
-          <t>仙人掌战士</t>
-        </is>
-      </c>
-      <c r="F315" s="18" t="inlineStr">
-        <is>
-          <t>Cactus Warrior</t>
+      <c r="A315" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B315" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr"/>
+      <c r="D315" s="20" t="inlineStr">
+        <is>
+          <t>熔岩</t>
+        </is>
+      </c>
+      <c r="E315" s="20" t="inlineStr">
+        <is>
+          <t>熔岩</t>
+        </is>
+      </c>
+      <c r="F315" s="20" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B316" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C316" s="18" t="n"/>
-      <c r="D316" s="18" t="inlineStr">
-        <is>
-          <t>大雪人</t>
-        </is>
-      </c>
-      <c r="E316" s="18" t="inlineStr">
-        <is>
-          <t>大雪人</t>
-        </is>
-      </c>
-      <c r="F316" s="18" t="inlineStr">
-        <is>
-          <t>Big Snowman</t>
+      <c r="A316" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B316" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C316" s="20" t="inlineStr"/>
+      <c r="D316" s="20" t="inlineStr">
+        <is>
+          <t>神殿</t>
+        </is>
+      </c>
+      <c r="E316" s="20" t="inlineStr">
+        <is>
+          <t>神殿</t>
+        </is>
+      </c>
+      <c r="F316" s="20" t="inlineStr">
+        <is>
+          <t>Shrine</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B317" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C317" s="18" t="n"/>
-      <c r="D317" s="18" t="inlineStr">
-        <is>
-          <t>小仙人掌</t>
-        </is>
-      </c>
-      <c r="E317" s="18" t="inlineStr">
-        <is>
-          <t>小仙人掌</t>
-        </is>
-      </c>
-      <c r="F317" s="18" t="inlineStr">
-        <is>
-          <t>Little Cactus</t>
+      <c r="A317" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B317" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C317" s="20" t="inlineStr"/>
+      <c r="D317" s="20" t="inlineStr">
+        <is>
+          <t>道路</t>
+        </is>
+      </c>
+      <c r="E317" s="20" t="inlineStr">
+        <is>
+          <t>道路</t>
+        </is>
+      </c>
+      <c r="F317" s="20" t="inlineStr">
+        <is>
+          <t>Road</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B318" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C318" s="18" t="n"/>
-      <c r="D318" s="18" t="inlineStr">
-        <is>
-          <t>小石怪</t>
-        </is>
-      </c>
-      <c r="E318" s="18" t="inlineStr">
-        <is>
-          <t>小石怪</t>
-        </is>
-      </c>
-      <c r="F318" s="18" t="inlineStr">
-        <is>
-          <t>Little Rock</t>
+      <c r="A318" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B318" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AETerrain·ZhName</t>
+        </is>
+      </c>
+      <c r="C318" s="20" t="inlineStr"/>
+      <c r="D318" s="20" t="inlineStr">
+        <is>
+          <t>雪地</t>
+        </is>
+      </c>
+      <c r="E318" s="20" t="inlineStr">
+        <is>
+          <t>雪地</t>
+        </is>
+      </c>
+      <c r="F318" s="20" t="inlineStr">
+        <is>
+          <t>Snow</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B319" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C319" s="18" t="n"/>
-      <c r="D319" s="18" t="inlineStr">
-        <is>
-          <t>小雪人</t>
-        </is>
-      </c>
-      <c r="E319" s="18" t="inlineStr">
-        <is>
-          <t>小雪人</t>
-        </is>
-      </c>
-      <c r="F319" s="18" t="inlineStr">
-        <is>
-          <t>Little Snowman</t>
+      <c r="A319" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B319" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C319" s="20" t="inlineStr"/>
+      <c r="D319" s="20" t="inlineStr">
+        <is>
+          <t>指挥官</t>
+        </is>
+      </c>
+      <c r="E319" s="20" t="inlineStr">
+        <is>
+          <t>指挥官</t>
+        </is>
+      </c>
+      <c r="F319" s="20" t="inlineStr">
+        <is>
+          <t>Commander</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B320" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C320" s="18" t="n"/>
-      <c r="D320" s="18" t="inlineStr">
-        <is>
-          <t>木头人</t>
-        </is>
-      </c>
-      <c r="E320" s="18" t="inlineStr">
-        <is>
-          <t>木头人</t>
-        </is>
-      </c>
-      <c r="F320" s="18" t="inlineStr">
-        <is>
-          <t>Wooden Dummy</t>
+      <c r="A320" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B320" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C320" s="20" t="inlineStr"/>
+      <c r="D320" s="20" t="inlineStr">
+        <is>
+          <t>小不点</t>
+        </is>
+      </c>
+      <c r="E320" s="20" t="inlineStr">
+        <is>
+          <t>小不点</t>
+        </is>
+      </c>
+      <c r="F320" s="20" t="inlineStr">
+        <is>
+          <t>Wisp</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B321" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C321" s="18" t="n"/>
-      <c r="D321" s="18" t="inlineStr">
-        <is>
-          <t>石头人</t>
-        </is>
-      </c>
-      <c r="E321" s="18" t="inlineStr">
-        <is>
-          <t>石头人</t>
-        </is>
-      </c>
-      <c r="F321" s="18" t="inlineStr">
-        <is>
-          <t>Rock Man</t>
+      <c r="A321" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B321" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C321" s="20" t="inlineStr"/>
+      <c r="D321" s="20" t="inlineStr">
+        <is>
+          <t>投石车</t>
+        </is>
+      </c>
+      <c r="E321" s="20" t="inlineStr">
+        <is>
+          <t>投石车</t>
+        </is>
+      </c>
+      <c r="F321" s="20" t="inlineStr">
+        <is>
+          <t>Catapult</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B322" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWEnemy·ZhName</t>
-        </is>
-      </c>
-      <c r="C322" s="18" t="n"/>
-      <c r="D322" s="18" t="inlineStr">
-        <is>
-          <t>雪怪</t>
-        </is>
-      </c>
-      <c r="E322" s="18" t="inlineStr">
-        <is>
-          <t>雪怪</t>
-        </is>
-      </c>
-      <c r="F322" s="18" t="inlineStr">
-        <is>
-          <t>Yeti</t>
+      <c r="A322" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B322" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C322" s="20" t="inlineStr"/>
+      <c r="D322" s="20" t="inlineStr">
+        <is>
+          <t>水元素</t>
+        </is>
+      </c>
+      <c r="E322" s="20" t="inlineStr">
+        <is>
+          <t>水元素</t>
+        </is>
+      </c>
+      <c r="F322" s="20" t="inlineStr">
+        <is>
+          <t>Water Elemental</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B323" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWLevel·ZhName</t>
-        </is>
-      </c>
-      <c r="C323" s="18" t="n"/>
-      <c r="D323" s="18" t="inlineStr">
-        <is>
-          <t>冰雪山地</t>
-        </is>
-      </c>
-      <c r="E323" s="18" t="inlineStr">
-        <is>
-          <t>冰雪山地</t>
-        </is>
-      </c>
-      <c r="F323" s="18" t="inlineStr">
-        <is>
-          <t>Snow Mountain</t>
+      <c r="A323" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B323" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr"/>
+      <c r="D323" s="20" t="inlineStr">
+        <is>
+          <t>狼</t>
+        </is>
+      </c>
+      <c r="E323" s="20" t="inlineStr">
+        <is>
+          <t>狼</t>
+        </is>
+      </c>
+      <c r="F323" s="20" t="inlineStr">
+        <is>
+          <t>Wolf</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B324" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWLevel·ZhName</t>
-        </is>
-      </c>
-      <c r="C324" s="18" t="n"/>
-      <c r="D324" s="18" t="inlineStr">
-        <is>
-          <t>青草公园</t>
-        </is>
-      </c>
-      <c r="E324" s="18" t="inlineStr">
-        <is>
-          <t>青草公园</t>
-        </is>
-      </c>
-      <c r="F324" s="18" t="inlineStr">
-        <is>
-          <t>Grass Park</t>
+      <c r="A324" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B324" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C324" s="20" t="inlineStr"/>
+      <c r="D324" s="20" t="inlineStr">
+        <is>
+          <t>士兵</t>
+        </is>
+      </c>
+      <c r="E324" s="20" t="inlineStr">
+        <is>
+          <t>士兵</t>
+        </is>
+      </c>
+      <c r="F324" s="20" t="inlineStr">
+        <is>
+          <t>Soldier</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B325" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWMaterial·ZhName</t>
-        </is>
-      </c>
-      <c r="C325" s="18" t="n"/>
-      <c r="D325" s="18" t="inlineStr">
-        <is>
-          <t>冰雪</t>
-        </is>
-      </c>
-      <c r="E325" s="18" t="inlineStr">
-        <is>
-          <t>冰雪</t>
-        </is>
-      </c>
-      <c r="F325" s="18" t="inlineStr">
-        <is>
-          <t>Snow</t>
+      <c r="A325" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B325" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C325" s="20" t="inlineStr"/>
+      <c r="D325" s="20" t="inlineStr">
+        <is>
+          <t>弓箭手</t>
+        </is>
+      </c>
+      <c r="E325" s="20" t="inlineStr">
+        <is>
+          <t>弓箭手</t>
+        </is>
+      </c>
+      <c r="F325" s="20" t="inlineStr">
+        <is>
+          <t>Archer</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B326" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWMaterial·ZhName</t>
-        </is>
-      </c>
-      <c r="C326" s="18" t="n"/>
-      <c r="D326" s="18" t="inlineStr">
-        <is>
-          <t>岩浆</t>
-        </is>
-      </c>
-      <c r="E326" s="18" t="inlineStr">
-        <is>
-          <t>岩浆</t>
-        </is>
-      </c>
-      <c r="F326" s="18" t="inlineStr">
-        <is>
-          <t>Magma</t>
+      <c r="A326" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B326" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C326" s="20" t="inlineStr"/>
+      <c r="D326" s="20" t="inlineStr">
+        <is>
+          <t>飞龙</t>
+        </is>
+      </c>
+      <c r="E326" s="20" t="inlineStr">
+        <is>
+          <t>飞龙</t>
+        </is>
+      </c>
+      <c r="F326" s="20" t="inlineStr">
+        <is>
+          <t>Dragon</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B327" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWMaterial·ZhName</t>
-        </is>
-      </c>
-      <c r="C327" s="18" t="n"/>
-      <c r="D327" s="18" t="inlineStr">
-        <is>
-          <t>木头</t>
-        </is>
-      </c>
-      <c r="E327" s="18" t="inlineStr">
-        <is>
-          <t>木头</t>
-        </is>
-      </c>
-      <c r="F327" s="18" t="inlineStr">
-        <is>
-          <t>Wood</t>
+      <c r="A327" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B327" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C327" s="20" t="inlineStr"/>
+      <c r="D327" s="20" t="inlineStr">
+        <is>
+          <t>魔导士</t>
+        </is>
+      </c>
+      <c r="E327" s="20" t="inlineStr">
+        <is>
+          <t>魔导士</t>
+        </is>
+      </c>
+      <c r="F327" s="20" t="inlineStr">
+        <is>
+          <t>Wizard</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="18" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B328" s="18" t="inlineStr">
-        <is>
-          <t>配置表·AWMaterial·ZhName</t>
-        </is>
-      </c>
-      <c r="C328" s="18" t="n"/>
-      <c r="D328" s="18" t="inlineStr">
-        <is>
-          <t>沙子</t>
-        </is>
-      </c>
-      <c r="E328" s="18" t="inlineStr">
-        <is>
-          <t>沙子</t>
-        </is>
-      </c>
-      <c r="F328" s="18" t="inlineStr">
-        <is>
-          <t>Sand</t>
+      <c r="A328" s="20" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B328" s="20" t="inlineStr">
+        <is>
+          <t>配置表·AEUnit·ZhName</t>
+        </is>
+      </c>
+      <c r="C328" s="20" t="inlineStr"/>
+      <c r="D328" s="20" t="inlineStr">
+        <is>
+          <t>骷髅</t>
+        </is>
+      </c>
+      <c r="E328" s="20" t="inlineStr">
+        <is>
+          <t>骷髅</t>
+        </is>
+      </c>
+      <c r="F328" s="20" t="inlineStr">
+        <is>
+          <t>Skeleton</t>
         </is>
       </c>
     </row>
@@ -9712,23 +9715,23 @@
       </c>
       <c r="B329" s="18" t="inlineStr">
         <is>
-          <t>配置表·AWMaterial·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C329" s="18" t="n"/>
       <c r="D329" s="18" t="inlineStr">
         <is>
-          <t>流水</t>
+          <t>新手之臂</t>
         </is>
       </c>
       <c r="E329" s="18" t="inlineStr">
         <is>
-          <t>流水</t>
+          <t>新手之臂</t>
         </is>
       </c>
       <c r="F329" s="18" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Rookie Arm</t>
         </is>
       </c>
     </row>
@@ -9740,23 +9743,23 @@
       </c>
       <c r="B330" s="18" t="inlineStr">
         <is>
-          <t>配置表·AWMaterial·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C330" s="18" t="n"/>
       <c r="D330" s="18" t="inlineStr">
         <is>
-          <t>砖块</t>
+          <t>深渊之臂</t>
         </is>
       </c>
       <c r="E330" s="18" t="inlineStr">
         <is>
-          <t>砖块</t>
+          <t>深渊之臂</t>
         </is>
       </c>
       <c r="F330" s="18" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Abyss Arm</t>
         </is>
       </c>
     </row>
@@ -9768,23 +9771,23 @@
       </c>
       <c r="B331" s="18" t="inlineStr">
         <is>
-          <t>配置表·AWMaterial·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C331" s="18" t="n"/>
       <c r="D331" s="18" t="inlineStr">
         <is>
-          <t>草地</t>
+          <t>烈焰之臂</t>
         </is>
       </c>
       <c r="E331" s="18" t="inlineStr">
         <is>
-          <t>草地</t>
+          <t>烈焰之臂</t>
         </is>
       </c>
       <c r="F331" s="18" t="inlineStr">
         <is>
-          <t>Grass</t>
+          <t>Flame Arm</t>
         </is>
       </c>
     </row>
@@ -9796,23 +9799,23 @@
       </c>
       <c r="B332" s="18" t="inlineStr">
         <is>
-          <t>配置表·AWMaterial·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C332" s="18" t="n"/>
       <c r="D332" s="18" t="inlineStr">
         <is>
-          <t>金属</t>
+          <t>紫晶之臂</t>
         </is>
       </c>
       <c r="E332" s="18" t="inlineStr">
         <is>
-          <t>金属</t>
+          <t>紫晶之臂</t>
         </is>
       </c>
       <c r="F332" s="18" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Amethyst Arm</t>
         </is>
       </c>
     </row>
@@ -9824,23 +9827,23 @@
       </c>
       <c r="B333" s="18" t="inlineStr">
         <is>
-          <t>配置表·AWMaterial·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C333" s="18" t="n"/>
       <c r="D333" s="18" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>结实之臂</t>
         </is>
       </c>
       <c r="E333" s="18" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>结实之臂</t>
         </is>
       </c>
       <c r="F333" s="18" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Sturdy Arm</t>
         </is>
       </c>
     </row>
@@ -9852,23 +9855,23 @@
       </c>
       <c r="B334" s="18" t="inlineStr">
         <is>
-          <t>配置表·AWMaterial·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C334" s="18" t="n"/>
       <c r="D334" s="18" t="inlineStr">
         <is>
-          <t>霓虹</t>
+          <t>翡翠之臂</t>
         </is>
       </c>
       <c r="E334" s="18" t="inlineStr">
         <is>
-          <t>霓虹</t>
+          <t>翡翠之臂</t>
         </is>
       </c>
       <c r="F334" s="18" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Jade Arm</t>
         </is>
       </c>
     </row>
@@ -9880,23 +9883,23 @@
       </c>
       <c r="B335" s="18" t="inlineStr">
         <is>
-          <t>配置表·Enemy·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C335" s="18" t="n"/>
       <c r="D335" s="18" t="inlineStr">
         <is>
-          <t>近战哥布林</t>
+          <t>钢铁之臂</t>
         </is>
       </c>
       <c r="E335" s="18" t="inlineStr">
         <is>
-          <t>近战哥布林</t>
+          <t>钢铁之臂</t>
         </is>
       </c>
       <c r="F335" s="18" t="inlineStr">
         <is>
-          <t>Melee Goblin</t>
+          <t>Steel Arm</t>
         </is>
       </c>
     </row>
@@ -9908,23 +9911,23 @@
       </c>
       <c r="B336" s="18" t="inlineStr">
         <is>
-          <t>配置表·ItemData·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C336" s="18" t="n"/>
       <c r="D336" s="18" t="inlineStr">
         <is>
-          <t>宝石</t>
+          <t>雷霆之臂</t>
         </is>
       </c>
       <c r="E336" s="18" t="inlineStr">
         <is>
-          <t>宝石</t>
+          <t>雷霆之臂</t>
         </is>
       </c>
       <c r="F336" s="18" t="inlineStr">
         <is>
-          <t>Gem</t>
+          <t>Thunder Arm</t>
         </is>
       </c>
     </row>
@@ -9936,23 +9939,23 @@
       </c>
       <c r="B337" s="18" t="inlineStr">
         <is>
-          <t>配置表·ItemData·ZhName</t>
+          <t>配置表·AWArm·ZhName</t>
         </is>
       </c>
       <c r="C337" s="18" t="n"/>
       <c r="D337" s="18" t="inlineStr">
         <is>
-          <t>金钱</t>
+          <t>青铜之臂</t>
         </is>
       </c>
       <c r="E337" s="18" t="inlineStr">
         <is>
-          <t>金钱</t>
+          <t>青铜之臂</t>
         </is>
       </c>
       <c r="F337" s="18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bronze Arm</t>
         </is>
       </c>
     </row>
@@ -9964,23 +9967,23 @@
       </c>
       <c r="B338" s="18" t="inlineStr">
         <is>
-          <t>配置表·Mount·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C338" s="18" t="n"/>
       <c r="D338" s="18" t="inlineStr">
         <is>
-          <t>测试吉普</t>
+          <t>仙人掌之王</t>
         </is>
       </c>
       <c r="E338" s="18" t="inlineStr">
         <is>
-          <t>测试吉普</t>
+          <t>仙人掌之王</t>
         </is>
       </c>
       <c r="F338" s="18" t="inlineStr">
         <is>
-          <t>Test Jeep</t>
+          <t>Cactus King</t>
         </is>
       </c>
     </row>
@@ -9992,23 +9995,23 @@
       </c>
       <c r="B339" s="18" t="inlineStr">
         <is>
-          <t>配置表·Mount·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C339" s="18" t="n"/>
       <c r="D339" s="18" t="inlineStr">
         <is>
-          <t>测试直升机</t>
+          <t>仙人掌战士</t>
         </is>
       </c>
       <c r="E339" s="18" t="inlineStr">
         <is>
-          <t>测试直升机</t>
+          <t>仙人掌战士</t>
         </is>
       </c>
       <c r="F339" s="18" t="inlineStr">
         <is>
-          <t>Test Helicopter</t>
+          <t>Cactus Warrior</t>
         </is>
       </c>
     </row>
@@ -10020,23 +10023,23 @@
       </c>
       <c r="B340" s="18" t="inlineStr">
         <is>
-          <t>配置表·Mount·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C340" s="18" t="n"/>
       <c r="D340" s="18" t="inlineStr">
         <is>
-          <t>测试飞龙</t>
+          <t>大雪人</t>
         </is>
       </c>
       <c r="E340" s="18" t="inlineStr">
         <is>
-          <t>测试飞龙</t>
+          <t>大雪人</t>
         </is>
       </c>
       <c r="F340" s="18" t="inlineStr">
         <is>
-          <t>Test Dragon</t>
+          <t>Big Snowman</t>
         </is>
       </c>
     </row>
@@ -10048,23 +10051,23 @@
       </c>
       <c r="B341" s="18" t="inlineStr">
         <is>
-          <t>配置表·Mount·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C341" s="18" t="n"/>
       <c r="D341" s="18" t="inlineStr">
         <is>
-          <t>独角兽</t>
+          <t>小仙人掌</t>
         </is>
       </c>
       <c r="E341" s="18" t="inlineStr">
         <is>
-          <t>独角兽</t>
+          <t>小仙人掌</t>
         </is>
       </c>
       <c r="F341" s="18" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Little Cactus</t>
         </is>
       </c>
     </row>
@@ -10076,23 +10079,23 @@
       </c>
       <c r="B342" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C342" s="18" t="n"/>
       <c r="D342" s="18" t="inlineStr">
         <is>
-          <t>乒乓球兔</t>
+          <t>小石怪</t>
         </is>
       </c>
       <c r="E342" s="18" t="inlineStr">
         <is>
-          <t>乒乓球兔</t>
+          <t>小石怪</t>
         </is>
       </c>
       <c r="F342" s="18" t="inlineStr">
         <is>
-          <t>Ping Pong Rabbit</t>
+          <t>Little Rock</t>
         </is>
       </c>
     </row>
@@ -10104,23 +10107,23 @@
       </c>
       <c r="B343" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C343" s="18" t="n"/>
       <c r="D343" s="18" t="inlineStr">
         <is>
-          <t>书本熊</t>
+          <t>小雪人</t>
         </is>
       </c>
       <c r="E343" s="18" t="inlineStr">
         <is>
-          <t>书本熊</t>
+          <t>小雪人</t>
         </is>
       </c>
       <c r="F343" s="18" t="inlineStr">
         <is>
-          <t>Book Bear</t>
+          <t>Little Snowman</t>
         </is>
       </c>
     </row>
@@ -10132,23 +10135,23 @@
       </c>
       <c r="B344" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C344" s="18" t="n"/>
       <c r="D344" s="18" t="inlineStr">
         <is>
-          <t>兔子向导</t>
+          <t>木头人</t>
         </is>
       </c>
       <c r="E344" s="18" t="inlineStr">
         <is>
-          <t>兔子向导</t>
+          <t>木头人</t>
         </is>
       </c>
       <c r="F344" s="18" t="inlineStr">
         <is>
-          <t>Guide Rabbit</t>
+          <t>Wooden Dummy</t>
         </is>
       </c>
     </row>
@@ -10160,23 +10163,23 @@
       </c>
       <c r="B345" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C345" s="18" t="n"/>
       <c r="D345" s="18" t="inlineStr">
         <is>
-          <t>博士猴</t>
+          <t>石头人</t>
         </is>
       </c>
       <c r="E345" s="18" t="inlineStr">
         <is>
-          <t>博士猴</t>
+          <t>石头人</t>
         </is>
       </c>
       <c r="F345" s="18" t="inlineStr">
         <is>
-          <t>Doctor Monkey</t>
+          <t>Rock Man</t>
         </is>
       </c>
     </row>
@@ -10188,23 +10191,23 @@
       </c>
       <c r="B346" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWEnemy·ZhName</t>
         </is>
       </c>
       <c r="C346" s="18" t="n"/>
       <c r="D346" s="18" t="inlineStr">
         <is>
-          <t>寻宝豹</t>
+          <t>雪怪</t>
         </is>
       </c>
       <c r="E346" s="18" t="inlineStr">
         <is>
-          <t>寻宝豹</t>
+          <t>雪怪</t>
         </is>
       </c>
       <c r="F346" s="18" t="inlineStr">
         <is>
-          <t>Treasure Leopard</t>
+          <t>Yeti</t>
         </is>
       </c>
     </row>
@@ -10216,23 +10219,23 @@
       </c>
       <c r="B347" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWLevel·ZhName</t>
         </is>
       </c>
       <c r="C347" s="18" t="n"/>
       <c r="D347" s="18" t="inlineStr">
         <is>
-          <t>尺子豹</t>
+          <t>冰雪山地</t>
         </is>
       </c>
       <c r="E347" s="18" t="inlineStr">
         <is>
-          <t>尺子豹</t>
+          <t>冰雪山地</t>
         </is>
       </c>
       <c r="F347" s="18" t="inlineStr">
         <is>
-          <t>Ruler Leopard</t>
+          <t>Snow Mountain</t>
         </is>
       </c>
     </row>
@@ -10244,23 +10247,23 @@
       </c>
       <c r="B348" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWLevel·ZhName</t>
         </is>
       </c>
       <c r="C348" s="18" t="n"/>
       <c r="D348" s="18" t="inlineStr">
         <is>
-          <t>排球狗</t>
+          <t>青草公园</t>
         </is>
       </c>
       <c r="E348" s="18" t="inlineStr">
         <is>
-          <t>排球狗</t>
+          <t>青草公园</t>
         </is>
       </c>
       <c r="F348" s="18" t="inlineStr">
         <is>
-          <t>Volleyball Dog</t>
+          <t>Grass Park</t>
         </is>
       </c>
     </row>
@@ -10272,23 +10275,23 @@
       </c>
       <c r="B349" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C349" s="18" t="n"/>
       <c r="D349" s="18" t="inlineStr">
         <is>
-          <t>探险松鼠</t>
+          <t>冰雪</t>
         </is>
       </c>
       <c r="E349" s="18" t="inlineStr">
         <is>
-          <t>探险松鼠</t>
+          <t>冰雪</t>
         </is>
       </c>
       <c r="F349" s="18" t="inlineStr">
         <is>
-          <t>Explorer Squirrel</t>
+          <t>Snow</t>
         </is>
       </c>
     </row>
@@ -10300,23 +10303,23 @@
       </c>
       <c r="B350" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C350" s="18" t="n"/>
       <c r="D350" s="18" t="inlineStr">
         <is>
-          <t>矿工猫猫</t>
+          <t>岩浆</t>
         </is>
       </c>
       <c r="E350" s="18" t="inlineStr">
         <is>
-          <t>矿工猫猫</t>
+          <t>岩浆</t>
         </is>
       </c>
       <c r="F350" s="18" t="inlineStr">
         <is>
-          <t>Miner Cat</t>
+          <t>Magma</t>
         </is>
       </c>
     </row>
@@ -10328,23 +10331,23 @@
       </c>
       <c r="B351" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C351" s="18" t="n"/>
       <c r="D351" s="18" t="inlineStr">
         <is>
-          <t>篮球熊</t>
+          <t>木头</t>
         </is>
       </c>
       <c r="E351" s="18" t="inlineStr">
         <is>
-          <t>篮球熊</t>
+          <t>木头</t>
         </is>
       </c>
       <c r="F351" s="18" t="inlineStr">
         <is>
-          <t>Basketball Bear</t>
+          <t>Wood</t>
         </is>
       </c>
     </row>
@@ -10356,23 +10359,23 @@
       </c>
       <c r="B352" s="18" t="inlineStr">
         <is>
-          <t>配置表·Pet·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C352" s="18" t="n"/>
       <c r="D352" s="18" t="inlineStr">
         <is>
-          <t>铅笔蜂</t>
+          <t>沙子</t>
         </is>
       </c>
       <c r="E352" s="18" t="inlineStr">
         <is>
-          <t>铅笔蜂</t>
+          <t>沙子</t>
         </is>
       </c>
       <c r="F352" s="18" t="inlineStr">
         <is>
-          <t>Pencil Bee</t>
+          <t>Sand</t>
         </is>
       </c>
     </row>
@@ -10384,23 +10387,23 @@
       </c>
       <c r="B353" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhDes</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C353" s="18" t="n"/>
       <c r="D353" s="18" t="inlineStr">
         <is>
-          <t>锁定当前目标</t>
+          <t>流水</t>
         </is>
       </c>
       <c r="E353" s="18" t="inlineStr">
         <is>
-          <t>锁定当前目标</t>
+          <t>流水</t>
         </is>
       </c>
       <c r="F353" s="18" t="inlineStr">
         <is>
-          <t>Current Target</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -10412,23 +10415,23 @@
       </c>
       <c r="B354" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhDes</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C354" s="18" t="n"/>
       <c r="D354" s="18" t="inlineStr">
         <is>
-          <t>锁定最近目标</t>
+          <t>砖块</t>
         </is>
       </c>
       <c r="E354" s="18" t="inlineStr">
         <is>
-          <t>锁定最近目标</t>
+          <t>砖块</t>
         </is>
       </c>
       <c r="F354" s="18" t="inlineStr">
         <is>
-          <t>Nearest Target</t>
+          <t>Brick</t>
         </is>
       </c>
     </row>
@@ -10440,23 +10443,23 @@
       </c>
       <c r="B355" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C355" s="18" t="n"/>
       <c r="D355" s="18" t="inlineStr">
         <is>
-          <t>任务</t>
+          <t>草地</t>
         </is>
       </c>
       <c r="E355" s="18" t="inlineStr">
         <is>
-          <t>任务</t>
+          <t>草地</t>
         </is>
       </c>
       <c r="F355" s="18" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Grass</t>
         </is>
       </c>
     </row>
@@ -10468,23 +10471,23 @@
       </c>
       <c r="B356" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C356" s="18" t="n"/>
       <c r="D356" s="18" t="inlineStr">
         <is>
-          <t>图像质量</t>
+          <t>金属</t>
         </is>
       </c>
       <c r="E356" s="18" t="inlineStr">
         <is>
-          <t>图像质量</t>
+          <t>金属</t>
         </is>
       </c>
       <c r="F356" s="18" t="inlineStr">
         <is>
-          <t>Graphics Quality</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -10496,23 +10499,23 @@
       </c>
       <c r="B357" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C357" s="18" t="n"/>
       <c r="D357" s="18" t="inlineStr">
         <is>
-          <t>奔跑模式</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="E357" s="18" t="inlineStr">
         <is>
-          <t>奔跑模式</t>
+          <t>钻石</t>
         </is>
       </c>
       <c r="F357" s="18" t="inlineStr">
         <is>
-          <t>Run Mode</t>
+          <t>Diamond</t>
         </is>
       </c>
     </row>
@@ -10524,23 +10527,23 @@
       </c>
       <c r="B358" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·AWMaterial·ZhName</t>
         </is>
       </c>
       <c r="C358" s="18" t="n"/>
       <c r="D358" s="18" t="inlineStr">
         <is>
-          <t>屏幕震动</t>
+          <t>霓虹</t>
         </is>
       </c>
       <c r="E358" s="18" t="inlineStr">
         <is>
-          <t>屏幕震动</t>
+          <t>霓虹</t>
         </is>
       </c>
       <c r="F358" s="18" t="inlineStr">
         <is>
-          <t>Screen Shake</t>
+          <t>Neon</t>
         </is>
       </c>
     </row>
@@ -10552,23 +10555,23 @@
       </c>
       <c r="B359" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Enemy·ZhName</t>
         </is>
       </c>
       <c r="C359" s="18" t="n"/>
       <c r="D359" s="18" t="inlineStr">
         <is>
-          <t>快捷栏尺寸</t>
+          <t>近战哥布林</t>
         </is>
       </c>
       <c r="E359" s="18" t="inlineStr">
         <is>
-          <t>快捷栏尺寸</t>
+          <t>近战哥布林</t>
         </is>
       </c>
       <c r="F359" s="18" t="inlineStr">
         <is>
-          <t>Hotbar Size</t>
+          <t>Melee Goblin</t>
         </is>
       </c>
     </row>
@@ -10580,23 +10583,23 @@
       </c>
       <c r="B360" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·ItemData·ZhName</t>
         </is>
       </c>
       <c r="C360" s="18" t="n"/>
       <c r="D360" s="18" t="inlineStr">
         <is>
-          <t>掉落物模型</t>
+          <t>宝石</t>
         </is>
       </c>
       <c r="E360" s="18" t="inlineStr">
         <is>
-          <t>掉落物模型</t>
+          <t>宝石</t>
         </is>
       </c>
       <c r="F360" s="18" t="inlineStr">
         <is>
-          <t>Loot Models</t>
+          <t>Gem</t>
         </is>
       </c>
     </row>
@@ -10608,23 +10611,23 @@
       </c>
       <c r="B361" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·ItemData·ZhName</t>
         </is>
       </c>
       <c r="C361" s="18" t="n"/>
       <c r="D361" s="18" t="inlineStr">
         <is>
-          <t>显示他人信息</t>
+          <t>金钱</t>
         </is>
       </c>
       <c r="E361" s="18" t="inlineStr">
         <is>
-          <t>显示他人信息</t>
+          <t>金钱</t>
         </is>
       </c>
       <c r="F361" s="18" t="inlineStr">
         <is>
-          <t>Show Player Info</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -10636,23 +10639,23 @@
       </c>
       <c r="B362" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Mount·ZhName</t>
         </is>
       </c>
       <c r="C362" s="18" t="n"/>
       <c r="D362" s="18" t="inlineStr">
         <is>
-          <t>游戏音效</t>
+          <t>测试吉普</t>
         </is>
       </c>
       <c r="E362" s="18" t="inlineStr">
         <is>
-          <t>游戏音效</t>
+          <t>测试吉普</t>
         </is>
       </c>
       <c r="F362" s="18" t="inlineStr">
         <is>
-          <t>SFX Volume</t>
+          <t>Test Jeep</t>
         </is>
       </c>
     </row>
@@ -10664,23 +10667,23 @@
       </c>
       <c r="B363" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Mount·ZhName</t>
         </is>
       </c>
       <c r="C363" s="18" t="n"/>
       <c r="D363" s="18" t="inlineStr">
         <is>
-          <t>物理效果</t>
+          <t>测试直升机</t>
         </is>
       </c>
       <c r="E363" s="18" t="inlineStr">
         <is>
-          <t>物理效果</t>
+          <t>测试直升机</t>
         </is>
       </c>
       <c r="F363" s="18" t="inlineStr">
         <is>
-          <t>Physics Effects</t>
+          <t>Test Helicopter</t>
         </is>
       </c>
     </row>
@@ -10692,23 +10695,23 @@
       </c>
       <c r="B364" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Mount·ZhName</t>
         </is>
       </c>
       <c r="C364" s="18" t="n"/>
       <c r="D364" s="18" t="inlineStr">
         <is>
-          <t>用户界面</t>
+          <t>测试飞龙</t>
         </is>
       </c>
       <c r="E364" s="18" t="inlineStr">
         <is>
-          <t>用户界面</t>
+          <t>测试飞龙</t>
         </is>
       </c>
       <c r="F364" s="18" t="inlineStr">
         <is>
-          <t>UI Visibility</t>
+          <t>Test Dragon</t>
         </is>
       </c>
     </row>
@@ -10720,23 +10723,23 @@
       </c>
       <c r="B365" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Mount·ZhName</t>
         </is>
       </c>
       <c r="C365" s="18" t="n"/>
       <c r="D365" s="18" t="inlineStr">
         <is>
-          <t>界面尺寸</t>
+          <t>独角兽</t>
         </is>
       </c>
       <c r="E365" s="18" t="inlineStr">
         <is>
-          <t>界面尺寸</t>
+          <t>独角兽</t>
         </is>
       </c>
       <c r="F365" s="18" t="inlineStr">
         <is>
-          <t>UI Scale</t>
+          <t>Unicorn</t>
         </is>
       </c>
     </row>
@@ -10748,23 +10751,23 @@
       </c>
       <c r="B366" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C366" s="18" t="n"/>
       <c r="D366" s="18" t="inlineStr">
         <is>
-          <t>瞄准模式</t>
+          <t>乒乓球兔</t>
         </is>
       </c>
       <c r="E366" s="18" t="inlineStr">
         <is>
-          <t>瞄准模式</t>
+          <t>乒乓球兔</t>
         </is>
       </c>
       <c r="F366" s="18" t="inlineStr">
         <is>
-          <t>Aim Mode</t>
+          <t>Ping Pong Rabbit</t>
         </is>
       </c>
     </row>
@@ -10776,23 +10779,23 @@
       </c>
       <c r="B367" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C367" s="18" t="n"/>
       <c r="D367" s="18" t="inlineStr">
         <is>
-          <t>称号</t>
+          <t>书本熊</t>
         </is>
       </c>
       <c r="E367" s="18" t="inlineStr">
         <is>
-          <t>称号</t>
+          <t>书本熊</t>
         </is>
       </c>
       <c r="F367" s="18" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Book Bear</t>
         </is>
       </c>
     </row>
@@ -10804,23 +10807,23 @@
       </c>
       <c r="B368" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C368" s="18" t="n"/>
       <c r="D368" s="18" t="inlineStr">
         <is>
-          <t>背景音乐</t>
+          <t>兔子向导</t>
         </is>
       </c>
       <c r="E368" s="18" t="inlineStr">
         <is>
-          <t>背景音乐</t>
+          <t>兔子向导</t>
         </is>
       </c>
       <c r="F368" s="18" t="inlineStr">
         <is>
-          <t>Music Volume</t>
+          <t>Guide Rabbit</t>
         </is>
       </c>
     </row>
@@ -10832,23 +10835,23 @@
       </c>
       <c r="B369" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C369" s="18" t="n"/>
       <c r="D369" s="18" t="inlineStr">
         <is>
-          <t>自动加点</t>
+          <t>博士猴</t>
         </is>
       </c>
       <c r="E369" s="18" t="inlineStr">
         <is>
-          <t>自动加点</t>
+          <t>博士猴</t>
         </is>
       </c>
       <c r="F369" s="18" t="inlineStr">
         <is>
-          <t>Auto Stat Points</t>
+          <t>Doctor Monkey</t>
         </is>
       </c>
     </row>
@@ -10860,23 +10863,23 @@
       </c>
       <c r="B370" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C370" s="18" t="n"/>
       <c r="D370" s="18" t="inlineStr">
         <is>
-          <t>自动锁敌</t>
+          <t>寻宝豹</t>
         </is>
       </c>
       <c r="E370" s="18" t="inlineStr">
         <is>
-          <t>自动锁敌</t>
+          <t>寻宝豹</t>
         </is>
       </c>
       <c r="F370" s="18" t="inlineStr">
         <is>
-          <t>Auto-Targeting</t>
+          <t>Treasure Leopard</t>
         </is>
       </c>
     </row>
@@ -10888,23 +10891,23 @@
       </c>
       <c r="B371" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C371" s="18" t="n"/>
       <c r="D371" s="18" t="inlineStr">
         <is>
-          <t>视野范围</t>
+          <t>尺子豹</t>
         </is>
       </c>
       <c r="E371" s="18" t="inlineStr">
         <is>
-          <t>视野范围</t>
+          <t>尺子豹</t>
         </is>
       </c>
       <c r="F371" s="18" t="inlineStr">
         <is>
-          <t>Field of View</t>
+          <t>Ruler Leopard</t>
         </is>
       </c>
     </row>
@@ -10916,23 +10919,23 @@
       </c>
       <c r="B372" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C372" s="18" t="n"/>
       <c r="D372" s="18" t="inlineStr">
         <is>
-          <t>记忆快速炼金</t>
+          <t>排球狗</t>
         </is>
       </c>
       <c r="E372" s="18" t="inlineStr">
         <is>
-          <t>记忆快速炼金</t>
+          <t>排球狗</t>
         </is>
       </c>
       <c r="F372" s="18" t="inlineStr">
         <is>
-          <t>Quick Alchemy Memory</t>
+          <t>Volleyball Dog</t>
         </is>
       </c>
     </row>
@@ -10944,23 +10947,23 @@
       </c>
       <c r="B373" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C373" s="18" t="n"/>
       <c r="D373" s="18" t="inlineStr">
         <is>
-          <t>长按攻击</t>
+          <t>探险松鼠</t>
         </is>
       </c>
       <c r="E373" s="18" t="inlineStr">
         <is>
-          <t>长按攻击</t>
+          <t>探险松鼠</t>
         </is>
       </c>
       <c r="F373" s="18" t="inlineStr">
         <is>
-          <t>Hold to Attack</t>
+          <t>Explorer Squirrel</t>
         </is>
       </c>
     </row>
@@ -10972,23 +10975,23 @@
       </c>
       <c r="B374" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C374" s="18" t="n"/>
       <c r="D374" s="18" t="inlineStr">
         <is>
-          <t>隐藏头部饰品</t>
+          <t>矿工猫猫</t>
         </is>
       </c>
       <c r="E374" s="18" t="inlineStr">
         <is>
-          <t>隐藏头部饰品</t>
+          <t>矿工猫猫</t>
         </is>
       </c>
       <c r="F374" s="18" t="inlineStr">
         <is>
-          <t>Hide Head Accessories</t>
+          <t>Miner Cat</t>
         </is>
       </c>
     </row>
@@ -11000,23 +11003,23 @@
       </c>
       <c r="B375" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C375" s="18" t="n"/>
       <c r="D375" s="18" t="inlineStr">
         <is>
-          <t>隐藏巫师袍</t>
+          <t>篮球熊</t>
         </is>
       </c>
       <c r="E375" s="18" t="inlineStr">
         <is>
-          <t>隐藏魔法袍</t>
+          <t>篮球熊</t>
         </is>
       </c>
       <c r="F375" s="18" t="inlineStr">
         <is>
-          <t>Hide Wizard Robe</t>
+          <t>Basketball Bear</t>
         </is>
       </c>
     </row>
@@ -11028,23 +11031,23 @@
       </c>
       <c r="B376" s="18" t="inlineStr">
         <is>
-          <t>配置表·Setting·ZhName</t>
+          <t>配置表·Pet·ZhName</t>
         </is>
       </c>
       <c r="C376" s="18" t="n"/>
       <c r="D376" s="18" t="inlineStr">
         <is>
-          <t>隐藏种族外观</t>
+          <t>铅笔蜂</t>
         </is>
       </c>
       <c r="E376" s="18" t="inlineStr">
         <is>
-          <t>隐藏种族外观</t>
+          <t>铅笔蜂</t>
         </is>
       </c>
       <c r="F376" s="18" t="inlineStr">
         <is>
-          <t>Hide racial appearance</t>
+          <t>Pencil Bee</t>
         </is>
       </c>
     </row>
@@ -11056,23 +11059,23 @@
       </c>
       <c r="B377" s="18" t="inlineStr">
         <is>
-          <t>配置表·Skill·ZhName</t>
+          <t>配置表·Setting·ZhDes</t>
         </is>
       </c>
       <c r="C377" s="18" t="n"/>
       <c r="D377" s="18" t="inlineStr">
         <is>
-          <t>冲刺</t>
+          <t>锁定当前目标</t>
         </is>
       </c>
       <c r="E377" s="18" t="inlineStr">
         <is>
-          <t>冲刺</t>
+          <t>锁定当前目标</t>
         </is>
       </c>
       <c r="F377" s="18" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Current Target</t>
         </is>
       </c>
     </row>
@@ -11084,23 +11087,23 @@
       </c>
       <c r="B378" s="18" t="inlineStr">
         <is>
-          <t>配置表·Skill·ZhName</t>
+          <t>配置表·Setting·ZhDes</t>
         </is>
       </c>
       <c r="C378" s="18" t="n"/>
       <c r="D378" s="18" t="inlineStr">
         <is>
-          <t>演示施法</t>
+          <t>锁定最近目标</t>
         </is>
       </c>
       <c r="E378" s="18" t="inlineStr">
         <is>
-          <t>演示施法</t>
+          <t>锁定最近目标</t>
         </is>
       </c>
       <c r="F378" s="18" t="inlineStr">
         <is>
-          <t>Demo Cast</t>
+          <t>Nearest Target</t>
         </is>
       </c>
     </row>
@@ -11112,217 +11115,1280 @@
       </c>
       <c r="B379" s="18" t="inlineStr">
         <is>
-          <t>配置表·Skill·ZhName</t>
+          <t>配置表·Setting·ZhName</t>
         </is>
       </c>
       <c r="C379" s="18" t="n"/>
       <c r="D379" s="18" t="inlineStr">
         <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="E379" s="18" t="inlineStr">
+        <is>
+          <t>任务</t>
+        </is>
+      </c>
+      <c r="F379" s="18" t="inlineStr">
+        <is>
+          <t>Quests</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B380" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C380" s="18" t="n"/>
+      <c r="D380" s="18" t="inlineStr">
+        <is>
+          <t>图像质量</t>
+        </is>
+      </c>
+      <c r="E380" s="18" t="inlineStr">
+        <is>
+          <t>图像质量</t>
+        </is>
+      </c>
+      <c r="F380" s="18" t="inlineStr">
+        <is>
+          <t>Graphics Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B381" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C381" s="18" t="n"/>
+      <c r="D381" s="18" t="inlineStr">
+        <is>
+          <t>奔跑模式</t>
+        </is>
+      </c>
+      <c r="E381" s="18" t="inlineStr">
+        <is>
+          <t>奔跑模式</t>
+        </is>
+      </c>
+      <c r="F381" s="18" t="inlineStr">
+        <is>
+          <t>Run Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B382" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C382" s="18" t="n"/>
+      <c r="D382" s="18" t="inlineStr">
+        <is>
+          <t>屏幕震动</t>
+        </is>
+      </c>
+      <c r="E382" s="18" t="inlineStr">
+        <is>
+          <t>屏幕震动</t>
+        </is>
+      </c>
+      <c r="F382" s="18" t="inlineStr">
+        <is>
+          <t>Screen Shake</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B383" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C383" s="18" t="n"/>
+      <c r="D383" s="18" t="inlineStr">
+        <is>
+          <t>快捷栏尺寸</t>
+        </is>
+      </c>
+      <c r="E383" s="18" t="inlineStr">
+        <is>
+          <t>快捷栏尺寸</t>
+        </is>
+      </c>
+      <c r="F383" s="18" t="inlineStr">
+        <is>
+          <t>Hotbar Size</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B384" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C384" s="18" t="n"/>
+      <c r="D384" s="18" t="inlineStr">
+        <is>
+          <t>掉落物模型</t>
+        </is>
+      </c>
+      <c r="E384" s="18" t="inlineStr">
+        <is>
+          <t>掉落物模型</t>
+        </is>
+      </c>
+      <c r="F384" s="18" t="inlineStr">
+        <is>
+          <t>Loot Models</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B385" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C385" s="18" t="n"/>
+      <c r="D385" s="18" t="inlineStr">
+        <is>
+          <t>显示他人信息</t>
+        </is>
+      </c>
+      <c r="E385" s="18" t="inlineStr">
+        <is>
+          <t>显示他人信息</t>
+        </is>
+      </c>
+      <c r="F385" s="18" t="inlineStr">
+        <is>
+          <t>Show Player Info</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B386" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C386" s="18" t="n"/>
+      <c r="D386" s="18" t="inlineStr">
+        <is>
+          <t>游戏音效</t>
+        </is>
+      </c>
+      <c r="E386" s="18" t="inlineStr">
+        <is>
+          <t>游戏音效</t>
+        </is>
+      </c>
+      <c r="F386" s="18" t="inlineStr">
+        <is>
+          <t>SFX Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B387" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C387" s="18" t="n"/>
+      <c r="D387" s="18" t="inlineStr">
+        <is>
+          <t>物理效果</t>
+        </is>
+      </c>
+      <c r="E387" s="18" t="inlineStr">
+        <is>
+          <t>物理效果</t>
+        </is>
+      </c>
+      <c r="F387" s="18" t="inlineStr">
+        <is>
+          <t>Physics Effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B388" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C388" s="18" t="n"/>
+      <c r="D388" s="18" t="inlineStr">
+        <is>
+          <t>用户界面</t>
+        </is>
+      </c>
+      <c r="E388" s="18" t="inlineStr">
+        <is>
+          <t>用户界面</t>
+        </is>
+      </c>
+      <c r="F388" s="18" t="inlineStr">
+        <is>
+          <t>UI Visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B389" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C389" s="18" t="n"/>
+      <c r="D389" s="18" t="inlineStr">
+        <is>
+          <t>界面尺寸</t>
+        </is>
+      </c>
+      <c r="E389" s="18" t="inlineStr">
+        <is>
+          <t>界面尺寸</t>
+        </is>
+      </c>
+      <c r="F389" s="18" t="inlineStr">
+        <is>
+          <t>UI Scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B390" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C390" s="18" t="n"/>
+      <c r="D390" s="18" t="inlineStr">
+        <is>
+          <t>瞄准模式</t>
+        </is>
+      </c>
+      <c r="E390" s="18" t="inlineStr">
+        <is>
+          <t>瞄准模式</t>
+        </is>
+      </c>
+      <c r="F390" s="18" t="inlineStr">
+        <is>
+          <t>Aim Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B391" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C391" s="18" t="n"/>
+      <c r="D391" s="18" t="inlineStr">
+        <is>
+          <t>称号</t>
+        </is>
+      </c>
+      <c r="E391" s="18" t="inlineStr">
+        <is>
+          <t>称号</t>
+        </is>
+      </c>
+      <c r="F391" s="18" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B392" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C392" s="18" t="n"/>
+      <c r="D392" s="18" t="inlineStr">
+        <is>
+          <t>背景音乐</t>
+        </is>
+      </c>
+      <c r="E392" s="18" t="inlineStr">
+        <is>
+          <t>背景音乐</t>
+        </is>
+      </c>
+      <c r="F392" s="18" t="inlineStr">
+        <is>
+          <t>Music Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B393" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C393" s="18" t="n"/>
+      <c r="D393" s="18" t="inlineStr">
+        <is>
+          <t>自动加点</t>
+        </is>
+      </c>
+      <c r="E393" s="18" t="inlineStr">
+        <is>
+          <t>自动加点</t>
+        </is>
+      </c>
+      <c r="F393" s="18" t="inlineStr">
+        <is>
+          <t>Auto Stat Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B394" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C394" s="18" t="n"/>
+      <c r="D394" s="18" t="inlineStr">
+        <is>
+          <t>自动锁敌</t>
+        </is>
+      </c>
+      <c r="E394" s="18" t="inlineStr">
+        <is>
+          <t>自动锁敌</t>
+        </is>
+      </c>
+      <c r="F394" s="18" t="inlineStr">
+        <is>
+          <t>Auto-Targeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B395" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C395" s="18" t="n"/>
+      <c r="D395" s="18" t="inlineStr">
+        <is>
+          <t>视野范围</t>
+        </is>
+      </c>
+      <c r="E395" s="18" t="inlineStr">
+        <is>
+          <t>视野范围</t>
+        </is>
+      </c>
+      <c r="F395" s="18" t="inlineStr">
+        <is>
+          <t>Field of View</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B396" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C396" s="18" t="n"/>
+      <c r="D396" s="18" t="inlineStr">
+        <is>
+          <t>记忆快速炼金</t>
+        </is>
+      </c>
+      <c r="E396" s="18" t="inlineStr">
+        <is>
+          <t>记忆快速炼金</t>
+        </is>
+      </c>
+      <c r="F396" s="18" t="inlineStr">
+        <is>
+          <t>Quick Alchemy Memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B397" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C397" s="18" t="n"/>
+      <c r="D397" s="18" t="inlineStr">
+        <is>
+          <t>长按攻击</t>
+        </is>
+      </c>
+      <c r="E397" s="18" t="inlineStr">
+        <is>
+          <t>长按攻击</t>
+        </is>
+      </c>
+      <c r="F397" s="18" t="inlineStr">
+        <is>
+          <t>Hold to Attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B398" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C398" s="18" t="n"/>
+      <c r="D398" s="18" t="inlineStr">
+        <is>
+          <t>隐藏头部饰品</t>
+        </is>
+      </c>
+      <c r="E398" s="18" t="inlineStr">
+        <is>
+          <t>隐藏头部饰品</t>
+        </is>
+      </c>
+      <c r="F398" s="18" t="inlineStr">
+        <is>
+          <t>Hide Head Accessories</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B399" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C399" s="18" t="n"/>
+      <c r="D399" s="18" t="inlineStr">
+        <is>
+          <t>隐藏巫师袍</t>
+        </is>
+      </c>
+      <c r="E399" s="18" t="inlineStr">
+        <is>
+          <t>隐藏魔法袍</t>
+        </is>
+      </c>
+      <c r="F399" s="18" t="inlineStr">
+        <is>
+          <t>Hide Wizard Robe</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B400" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Setting·ZhName</t>
+        </is>
+      </c>
+      <c r="C400" s="18" t="n"/>
+      <c r="D400" s="18" t="inlineStr">
+        <is>
+          <t>隐藏种族外观</t>
+        </is>
+      </c>
+      <c r="E400" s="18" t="inlineStr">
+        <is>
+          <t>隐藏种族外观</t>
+        </is>
+      </c>
+      <c r="F400" s="18" t="inlineStr">
+        <is>
+          <t>Hide racial appearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B401" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Skill·ZhName</t>
+        </is>
+      </c>
+      <c r="C401" s="18" t="n"/>
+      <c r="D401" s="18" t="inlineStr">
+        <is>
+          <t>冲刺</t>
+        </is>
+      </c>
+      <c r="E401" s="18" t="inlineStr">
+        <is>
+          <t>冲刺</t>
+        </is>
+      </c>
+      <c r="F401" s="18" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B402" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Skill·ZhName</t>
+        </is>
+      </c>
+      <c r="C402" s="18" t="n"/>
+      <c r="D402" s="18" t="inlineStr">
+        <is>
+          <t>演示施法</t>
+        </is>
+      </c>
+      <c r="E402" s="18" t="inlineStr">
+        <is>
+          <t>演示施法</t>
+        </is>
+      </c>
+      <c r="F402" s="18" t="inlineStr">
+        <is>
+          <t>Demo Cast</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="18" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B403" s="18" t="inlineStr">
+        <is>
+          <t>配置表·Skill·ZhName</t>
+        </is>
+      </c>
+      <c r="C403" s="18" t="n"/>
+      <c r="D403" s="18" t="inlineStr">
+        <is>
           <t>空间技能</t>
         </is>
       </c>
-      <c r="E379" s="18" t="inlineStr">
+      <c r="E403" s="18" t="inlineStr">
         <is>
           <t>空间技能</t>
         </is>
       </c>
-      <c r="F379" s="18" t="inlineStr">
+      <c r="F403" s="18" t="inlineStr">
         <is>
           <t>Space Skill</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" s="19" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B380" s="19" t="inlineStr">
+    <row r="404">
+      <c r="A404" s="19" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B404" s="19" t="inlineStr">
         <is>
           <t>配置表·Skill·ZhName</t>
         </is>
       </c>
-      <c r="C380" s="19" t="n"/>
-      <c r="D380" s="19" t="inlineStr">
+      <c r="C404" s="19" t="n"/>
+      <c r="D404" s="19" t="inlineStr">
         <is>
           <t>陨石术</t>
         </is>
       </c>
-      <c r="E380" s="19" t="inlineStr">
+      <c r="E404" s="19" t="inlineStr">
         <is>
           <t>陨石术</t>
         </is>
       </c>
-      <c r="F380" s="19" t="inlineStr">
+      <c r="F404" s="19" t="inlineStr">
         <is>
           <t>Meteor</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" s="19" t="inlineStr">
-        <is>
-          <t>05_配置名</t>
-        </is>
-      </c>
-      <c r="B381" s="19" t="inlineStr">
+    <row r="405">
+      <c r="A405" s="19" t="inlineStr">
+        <is>
+          <t>05_配置名</t>
+        </is>
+      </c>
+      <c r="B405" s="19" t="inlineStr">
         <is>
           <t>锁定全部按钮</t>
         </is>
       </c>
-      <c r="C381" s="19" t="n"/>
-      <c r="D381" s="19" t="inlineStr">
+      <c r="C405" s="19" t="n"/>
+      <c r="D405" s="19" t="inlineStr">
         <is>
           <t>锁定全部</t>
         </is>
       </c>
-      <c r="E381" s="19" t="inlineStr">
+      <c r="E405" s="19" t="inlineStr">
         <is>
           <t>锁定全部</t>
         </is>
       </c>
-      <c r="F381" s="19" t="inlineStr">
+      <c r="F405" s="19" t="inlineStr">
         <is>
           <t>Lock All</t>
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" s="19" t="inlineStr">
+    <row r="406">
+      <c r="A406" s="19" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B382" s="19" t="inlineStr">
+      <c r="B406" s="19" t="inlineStr">
         <is>
           <t>货币/宠物蛋等杂项 Key</t>
         </is>
       </c>
-      <c r="C382" s="19" t="n"/>
-      <c r="D382" s="19" t="inlineStr">
+      <c r="C406" s="19" t="n"/>
+      <c r="D406" s="19" t="inlineStr">
         <is>
           <t>Egg1</t>
         </is>
       </c>
-      <c r="E382" s="19" t="inlineStr">
+      <c r="E406" s="19" t="inlineStr">
         <is>
           <t>宠物蛋1</t>
         </is>
       </c>
-      <c r="F382" s="19" t="inlineStr">
+      <c r="F406" s="19" t="inlineStr">
         <is>
           <t>Egg 1</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" s="19" t="inlineStr">
+    <row r="407">
+      <c r="A407" s="19" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B383" s="19" t="inlineStr">
+      <c r="B407" s="19" t="inlineStr">
         <is>
           <t>货币/宠物蛋等杂项 Key</t>
         </is>
       </c>
-      <c r="C383" s="19" t="n"/>
-      <c r="D383" s="19" t="inlineStr">
+      <c r="C407" s="19" t="n"/>
+      <c r="D407" s="19" t="inlineStr">
         <is>
           <t>Egg2</t>
         </is>
       </c>
-      <c r="E383" s="19" t="inlineStr">
+      <c r="E407" s="19" t="inlineStr">
         <is>
           <t>宠物蛋2</t>
         </is>
       </c>
-      <c r="F383" s="19" t="inlineStr">
+      <c r="F407" s="19" t="inlineStr">
         <is>
           <t>Egg 2</t>
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" s="19" t="inlineStr">
+    <row r="408">
+      <c r="A408" s="19" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B384" s="19" t="inlineStr">
+      <c r="B408" s="19" t="inlineStr">
         <is>
           <t>货币/宠物蛋等杂项 Key</t>
         </is>
       </c>
-      <c r="C384" s="19" t="n"/>
-      <c r="D384" s="19" t="inlineStr">
+      <c r="C408" s="19" t="n"/>
+      <c r="D408" s="19" t="inlineStr">
         <is>
           <t>Egg3</t>
         </is>
       </c>
-      <c r="E384" s="19" t="inlineStr">
+      <c r="E408" s="19" t="inlineStr">
         <is>
           <t>宠物蛋3</t>
         </is>
       </c>
-      <c r="F384" s="19" t="inlineStr">
+      <c r="F408" s="19" t="inlineStr">
         <is>
           <t>Egg 3</t>
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>货币/宠物蛋等杂项 Key</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
+      <c r="D409" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
+      <c r="E409" t="inlineStr">
         <is>
           <t>宝石</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
+      <c r="F409" t="inlineStr">
         <is>
           <t>Gem</t>
         </is>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>货币/宠物蛋等杂项 Key</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
+      <c r="D410" t="inlineStr">
         <is>
           <t>zuanshi</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr">
+      <c r="E410" t="inlineStr">
         <is>
           <t>钻石</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr">
+      <c r="F410" t="inlineStr">
         <is>
           <t>Gems</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B411" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C411" s="20" t="inlineStr"/>
+      <c r="D411" s="20" t="inlineStr">
+        <is>
+          <t>再来一局</t>
+        </is>
+      </c>
+      <c r="E411" s="20" t="inlineStr">
+        <is>
+          <t>再来一局</t>
+        </is>
+      </c>
+      <c r="F411" s="20" t="inlineStr">
+        <is>
+          <t>Play Again</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B412" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C412" s="20" t="inlineStr"/>
+      <c r="D412" s="20" t="inlineStr">
+        <is>
+          <t>占领</t>
+        </is>
+      </c>
+      <c r="E412" s="20" t="inlineStr">
+        <is>
+          <t>占领</t>
+        </is>
+      </c>
+      <c r="F412" s="20" t="inlineStr">
+        <is>
+          <t>Occupy</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B413" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C413" s="20" t="inlineStr"/>
+      <c r="D413" s="20" t="inlineStr">
+        <is>
+          <t>击败敌军</t>
+        </is>
+      </c>
+      <c r="E413" s="20" t="inlineStr">
+        <is>
+          <t>击败全部敌军</t>
+        </is>
+      </c>
+      <c r="F413" s="20" t="inlineStr">
+        <is>
+          <t>Defeat all enemies</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B414" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C414" s="20" t="inlineStr"/>
+      <c r="D414" s="20" t="inlineStr">
+        <is>
+          <t>敌方回合</t>
+        </is>
+      </c>
+      <c r="E414" s="20" t="inlineStr">
+        <is>
+          <t>敌方回合</t>
+        </is>
+      </c>
+      <c r="F414" s="20" t="inlineStr">
+        <is>
+          <t>Enemy Turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B415" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C415" s="20" t="inlineStr"/>
+      <c r="D415" s="20" t="inlineStr">
+        <is>
+          <t>结束回合</t>
+        </is>
+      </c>
+      <c r="E415" s="20" t="inlineStr">
+        <is>
+          <t>结束回合</t>
+        </is>
+      </c>
+      <c r="F415" s="20" t="inlineStr">
+        <is>
+          <t>End Turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B416" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C416" s="20" t="inlineStr"/>
+      <c r="D416" s="20" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E416" s="20" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F416" s="20" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B417" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C417" s="20" t="inlineStr"/>
+      <c r="D417" s="20" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="E417" s="20" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="F417" s="20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B418" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C418" s="20" t="inlineStr"/>
+      <c r="D418" s="20" t="inlineStr">
+        <is>
+          <t>你的回合</t>
+        </is>
+      </c>
+      <c r="E418" s="20" t="inlineStr">
+        <is>
+          <t>你的回合</t>
+        </is>
+      </c>
+      <c r="F418" s="20" t="inlineStr">
+        <is>
+          <t>Your Turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B419" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C419" s="20" t="inlineStr"/>
+      <c r="D419" s="20" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="E419" s="20" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="F419" s="20" t="inlineStr">
+        <is>
+          <t>Defeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B420" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C420" s="20" t="inlineStr"/>
+      <c r="D420" s="20" t="inlineStr">
+        <is>
+          <t>生命</t>
+        </is>
+      </c>
+      <c r="E420" s="20" t="inlineStr">
+        <is>
+          <t>生命</t>
+        </is>
+      </c>
+      <c r="F420" s="20" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>无法开始对局</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>无法开始对局</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Cannot start match</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B422" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C422" s="20" t="inlineStr"/>
+      <c r="D422" s="20" t="inlineStr">
+        <is>
+          <t>招募</t>
+        </is>
+      </c>
+      <c r="E422" s="20" t="inlineStr">
+        <is>
+          <t>招募</t>
+        </is>
+      </c>
+      <c r="F422" s="20" t="inlineStr">
+        <is>
+          <t>Recruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B423" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C423" s="20" t="inlineStr"/>
+      <c r="D423" s="20" t="inlineStr">
+        <is>
+          <t>胜利</t>
+        </is>
+      </c>
+      <c r="E423" s="20" t="inlineStr">
+        <is>
+          <t>胜利</t>
+        </is>
+      </c>
+      <c r="F423" s="20" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B424" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C424" s="20" t="inlineStr"/>
+      <c r="D424" s="20" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="E424" s="20" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="F424" s="20" t="inlineStr">
+        <is>
+          <t>Move</t>
         </is>
       </c>
     </row>

--- a/config/Localization/LocalizationTable.xlsx
+++ b/config/Localization/LocalizationTable.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F424"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12254,85 +12254,84 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="20" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B420" s="20" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>战棋·HUD</t>
         </is>
       </c>
-      <c r="C420" s="20" t="inlineStr"/>
-      <c r="D420" s="20" t="inlineStr">
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>待命</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>待命</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B421" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C421" s="20" t="inlineStr"/>
+      <c r="D421" s="20" t="inlineStr">
         <is>
           <t>生命</t>
         </is>
       </c>
-      <c r="E420" s="20" t="inlineStr">
+      <c r="E421" s="20" t="inlineStr">
         <is>
           <t>生命</t>
         </is>
       </c>
-      <c r="F420" s="20" t="inlineStr">
+      <c r="F421" s="20" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t>06_其他</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>战棋·HUD</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D422" t="inlineStr">
         <is>
           <t>无法开始对局</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr">
+      <c r="E422" t="inlineStr">
         <is>
           <t>无法开始对局</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
+      <c r="F422" t="inlineStr">
         <is>
           <t>Cannot start match</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="20" t="inlineStr">
-        <is>
-          <t>06_其他</t>
-        </is>
-      </c>
-      <c r="B422" s="20" t="inlineStr">
-        <is>
-          <t>战棋·HUD</t>
-        </is>
-      </c>
-      <c r="C422" s="20" t="inlineStr"/>
-      <c r="D422" s="20" t="inlineStr">
-        <is>
-          <t>招募</t>
-        </is>
-      </c>
-      <c r="E422" s="20" t="inlineStr">
-        <is>
-          <t>招募</t>
-        </is>
-      </c>
-      <c r="F422" s="20" t="inlineStr">
-        <is>
-          <t>Recruit</t>
         </is>
       </c>
     </row>
@@ -12350,17 +12349,17 @@
       <c r="C423" s="20" t="inlineStr"/>
       <c r="D423" s="20" t="inlineStr">
         <is>
-          <t>胜利</t>
+          <t>招募</t>
         </is>
       </c>
       <c r="E423" s="20" t="inlineStr">
         <is>
-          <t>胜利</t>
+          <t>招募</t>
         </is>
       </c>
       <c r="F423" s="20" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Recruit</t>
         </is>
       </c>
     </row>
@@ -12378,15 +12377,43 @@
       <c r="C424" s="20" t="inlineStr"/>
       <c r="D424" s="20" t="inlineStr">
         <is>
+          <t>胜利</t>
+        </is>
+      </c>
+      <c r="E424" s="20" t="inlineStr">
+        <is>
+          <t>胜利</t>
+        </is>
+      </c>
+      <c r="F424" s="20" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="20" t="inlineStr">
+        <is>
+          <t>06_其他</t>
+        </is>
+      </c>
+      <c r="B425" s="20" t="inlineStr">
+        <is>
+          <t>战棋·HUD</t>
+        </is>
+      </c>
+      <c r="C425" s="20" t="inlineStr"/>
+      <c r="D425" s="20" t="inlineStr">
+        <is>
           <t>移动</t>
         </is>
       </c>
-      <c r="E424" s="20" t="inlineStr">
+      <c r="E425" s="20" t="inlineStr">
         <is>
           <t>移动</t>
         </is>
       </c>
-      <c r="F424" s="20" t="inlineStr">
+      <c r="F425" s="20" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
